--- a/docs/配置内容.xlsx
+++ b/docs/配置内容.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\魔法少女卡牌\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FCCB2B-F476-4784-B915-EF5AAB9D0B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87494AA-D865-4C70-8DB2-FE18F5AEFA3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="89">
   <si>
     <t>堕落的学生</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -374,6 +374,14 @@
   </si>
   <si>
     <t>循环</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -702,25 +710,31 @@
   <dimension ref="C2:S42"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="3:19" x14ac:dyDescent="0.2">
       <c r="D2" t="s">
         <v>0</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="Q2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="3:19" x14ac:dyDescent="0.2">
       <c r="D3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="S3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="3:19" x14ac:dyDescent="0.2">
       <c r="D4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C5" t="s">
         <v>4</v>
       </c>
@@ -728,22 +742,22 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="3:19" x14ac:dyDescent="0.2">
       <c r="D6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="3:19" x14ac:dyDescent="0.2">
       <c r="D7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="3:19" x14ac:dyDescent="0.2">
       <c r="D8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="3:19" x14ac:dyDescent="0.2">
       <c r="D16" t="s">
         <v>5</v>
       </c>

--- a/docs/配置内容.xlsx
+++ b/docs/配置内容.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\魔法少女卡牌\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87494AA-D865-4C70-8DB2-FE18F5AEFA3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA4A7A8-4D86-449D-9876-3C56213DDCD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9270" yWindow="2685" windowWidth="13095" windowHeight="11235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="堕落的学生" sheetId="3" r:id="rId2"/>
-    <sheet name="人物属性" sheetId="2" r:id="rId3"/>
+    <sheet name="关卡流程-学校" sheetId="4" r:id="rId2"/>
+    <sheet name="堕落的学生" sheetId="3" r:id="rId3"/>
+    <sheet name="人物属性" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="117">
   <si>
     <t>堕落的学生</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -382,6 +383,118 @@
   </si>
   <si>
     <t>时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一关 学校</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>流程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗奖励</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合 时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一段剧情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>位置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学校</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间过后也会结束这一天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不睡觉会疲惫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自慰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要发情值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡觉：结束这一天，降低疲劳值，会发情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用后降低发情值，提高敏感度，结束这一天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>洗澡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清楚身上的特殊效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>走廊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教室</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小卖铺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泳池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体育馆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>校长室</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教导室</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更衣室</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店街</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -936,157 +1049,133 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BC1711F-1F76-457C-8559-E9EAF9A4DDD8}">
-  <dimension ref="H5:K26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B349D95E-2D61-400D-8809-3E1D54E66EED}">
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="5" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H5" t="s">
-        <v>67</v>
-      </c>
-      <c r="I5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H8" t="s">
-        <v>68</v>
-      </c>
-      <c r="I8" t="s">
-        <v>69</v>
-      </c>
-      <c r="J8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="I9" t="s">
-        <v>70</v>
-      </c>
-      <c r="J9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="I10" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="J11" t="s">
-        <v>71</v>
-      </c>
-      <c r="K11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="K12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="K13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="I14" t="s">
-        <v>84</v>
-      </c>
-      <c r="J14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H15" t="s">
-        <v>73</v>
-      </c>
-      <c r="I15" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="I16" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H18" t="s">
-        <v>74</v>
-      </c>
-      <c r="I18" t="s">
-        <v>69</v>
-      </c>
-      <c r="J18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H21" t="s">
-        <v>77</v>
-      </c>
-      <c r="I21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="I22" t="s">
-        <v>79</v>
-      </c>
-      <c r="J22" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="I23" t="s">
-        <v>80</v>
-      </c>
-      <c r="J23" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="I24" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="I25" t="s">
-        <v>83</v>
-      </c>
-      <c r="J25" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="I26" t="s">
-        <v>86</v>
-      </c>
-      <c r="J26" t="s">
-        <v>84</v>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C21" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C22" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1097,6 +1186,167 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BC1711F-1F76-457C-8559-E9EAF9A4DDD8}">
+  <dimension ref="H5:K26"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="5" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="H5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="H6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="H8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="I9" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="I10" t="s">
+        <v>4</v>
+      </c>
+      <c r="J10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="J11" t="s">
+        <v>71</v>
+      </c>
+      <c r="K11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="K12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="K13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="I14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="H15" t="s">
+        <v>73</v>
+      </c>
+      <c r="I15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="I16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H18" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" t="s">
+        <v>69</v>
+      </c>
+      <c r="J18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I21" t="s">
+        <v>78</v>
+      </c>
+      <c r="J21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="I22" t="s">
+        <v>79</v>
+      </c>
+      <c r="J22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="I23" t="s">
+        <v>80</v>
+      </c>
+      <c r="J23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="I24" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="I25" t="s">
+        <v>83</v>
+      </c>
+      <c r="J25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="I26" t="s">
+        <v>86</v>
+      </c>
+      <c r="J26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6CC1BC4-8BA9-4BB2-938E-751AF391B831}">
   <dimension ref="B3:Q16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>

--- a/docs/配置内容.xlsx
+++ b/docs/配置内容.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\魔法少女卡牌\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA4A7A8-4D86-449D-9876-3C56213DDCD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{537D1E26-47EB-4EE7-9206-109FD2E1C645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9270" yWindow="2685" windowWidth="13095" windowHeight="11235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="126">
   <si>
     <t>堕落的学生</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -495,6 +495,42 @@
   </si>
   <si>
     <t>商店街</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>服装店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按摩店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇遇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四处逛逛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>起床</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果1-5不去学校，学校里的怪就会变厉害，并且催眠发生异变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有个学校的侵蚀计数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一次去学校会被下催眠，非周末一定要来学校</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1050,60 +1086,60 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B349D95E-2D61-400D-8809-3E1D54E66EED}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C13" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>97</v>
       </c>
@@ -1116,8 +1152,14 @@
       <c r="E14" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="J14" t="s">
+        <v>120</v>
+      </c>
+      <c r="K14" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C15" t="s">
         <v>102</v>
       </c>
@@ -1128,7 +1170,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C16" t="s">
         <v>106</v>
       </c>
@@ -1136,7 +1178,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>99</v>
       </c>
@@ -1147,7 +1189,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C19" t="s">
         <v>109</v>
       </c>
@@ -1155,7 +1197,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C20" t="s">
         <v>110</v>
       </c>
@@ -1163,19 +1205,52 @@
         <v>115</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H23" t="s">
+        <v>99</v>
+      </c>
+      <c r="I23" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>116</v>
+      </c>
+      <c r="C24" t="s">
+        <v>117</v>
+      </c>
+      <c r="H24" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="C25" t="s">
+        <v>118</v>
+      </c>
+      <c r="J25" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="C26" t="s">
+        <v>119</v>
+      </c>
+      <c r="J26" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
